--- a/artfynd/S 8435-2021 artfynd.xlsx
+++ b/artfynd/S 8435-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1990512</v>
+        <v>136802849</v>
       </c>
       <c r="B2" t="n">
-        <v>80432</v>
+        <v>97588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>4,8 km O om Skurträsk, Vb</t>
+          <t>Lidmyråsen domänreservat, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>702129</v>
+        <v>702171</v>
       </c>
       <c r="R2" t="n">
-        <v>7126494</v>
+        <v>7126361</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2005-07-26</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2005-07-26</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,66 +761,71 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>grov gammal tallåga</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Daniella Andersson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Daniella Andersson</t>
+          <t>Andreas Garpebring, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1990512</t>
+          <t>https://artportalen.se/Sighting/136802849</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112606413</v>
+        <v>136802851</v>
       </c>
       <c r="B3" t="n">
-        <v>99118</v>
+        <v>79508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skurträsk, Vb</t>
+          <t>Lidmyråsen domänreservat, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>702164</v>
+        <v>702142</v>
       </c>
       <c r="R3" t="n">
-        <v>7126380</v>
+        <v>7126367</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,17 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -866,68 +866,69 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Andreas Garpebring, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112606413</t>
+          <t>https://artportalen.se/Sighting/136802851</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133582981</v>
+        <v>136802854</v>
       </c>
       <c r="B4" t="n">
-        <v>99195</v>
+        <v>89336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skurträsk, Vb</t>
+          <t>Lidmyråsen domänreservat, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>702089</v>
+        <v>702076</v>
       </c>
       <c r="R4" t="n">
-        <v>7126417</v>
+        <v>7126419</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,17 +955,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,62 +975,62 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Andreas Garpebring, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133582981</t>
+          <t>https://artportalen.se/Sighting/136802854</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133582984</v>
+        <v>136802856</v>
       </c>
       <c r="B5" t="n">
-        <v>99195</v>
+        <v>92074</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skurträsk, Vb</t>
+          <t>Lidmyråsen domänreservat, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>702187</v>
+        <v>702075</v>
       </c>
       <c r="R5" t="n">
-        <v>7126371</v>
+        <v>7126421</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,17 +1057,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1082,22 +1073,3582 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Andreas Garpebring, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136802856</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136802852</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>702121</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7126411</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802852</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136802853</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>702109</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7126415</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802853</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136802859</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>702037</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7126433</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802859</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136802860</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>702033</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7126454</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802860</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136802862</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>702047</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7126480</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802862</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136802863</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>702059</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7126486</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802863</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136802866</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>702037</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7126531</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802866</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136802868</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>702055</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7126563</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802868</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136802870</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>702073</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7126561</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802870</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136802875</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>702117</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7126534</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802875</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136802876</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>702105</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7126530</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802876</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136802877</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>702095</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7126550</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802877</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136802878</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>702081</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7126534</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802878</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136802879</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>702081</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7126528</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802879</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136802881</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>702091</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7126501</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802881</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136802883</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>702130</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7126488</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802883</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136802884</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>702129</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7126460</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802884</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136802885</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>702111</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7126441</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802885</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136802886</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>702113</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7126430</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802886</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136802889</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>702164</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7126359</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802889</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136802857</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79500</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>702037</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7126419</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802857</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136802865</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79233</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>702057</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7126509</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>koald stubbe</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802865</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1990512</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>4,8 km O om Skurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>702129</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7126494</v>
+      </c>
+      <c r="S28" t="n">
+        <v>100</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2005-07-26</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2005-07-26</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Daniella Andersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Via Daniella Andersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1990512</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136802861</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>702046</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7126479</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802861</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136802867</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>702035</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7126529</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802867</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136802880</v>
+      </c>
+      <c r="B31" t="n">
+        <v>5498</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>702081</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7126517</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>gammeltall</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802880</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136802874</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>702120</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7126545</v>
+      </c>
+      <c r="S32" t="n">
+        <v>50</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802874</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136802864</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5202</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>702056</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7126512</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>död gran</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802864</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>112606413</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Skurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>702164</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7126380</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2022-10-05</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2022-10-05</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606413</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>133582981</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Skurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>702089</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7126417</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582981</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>133582984</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Skurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>702187</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7126371</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/133582984</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136802873</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>702116</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7126553</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802873</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>136802882</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>702093</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7126499</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802882</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>136802872</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98213</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lidmyråsen domänreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>702110</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7126560</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136802872</t>
         </is>
       </c>
     </row>
@@ -1107,6 +4658,40 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 8435-2021 artfynd.xlsx
+++ b/artfynd/S 8435-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136802849</v>
       </c>
       <c r="B2" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>136802854</v>
       </c>
       <c r="B4" t="n">
-        <v>89336</v>
+        <v>89338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>136802856</v>
       </c>
       <c r="B5" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>136802873</v>
       </c>
       <c r="B37" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>136802882</v>
       </c>
       <c r="B38" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>136802872</v>
       </c>
       <c r="B39" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/S 8435-2021 artfynd.xlsx
+++ b/artfynd/S 8435-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136802849</v>
       </c>
       <c r="B2" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136802851</v>
       </c>
       <c r="B3" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>136802854</v>
       </c>
       <c r="B4" t="n">
-        <v>89338</v>
+        <v>89340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>136802856</v>
       </c>
       <c r="B5" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>136802852</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>136802853</v>
       </c>
       <c r="B7" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>136802859</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>136802860</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>136802862</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>136802863</v>
       </c>
       <c r="B11" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>136802866</v>
       </c>
       <c r="B12" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>136802868</v>
       </c>
       <c r="B13" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136802870</v>
       </c>
       <c r="B14" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>136802875</v>
       </c>
       <c r="B15" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>136802876</v>
       </c>
       <c r="B16" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>136802877</v>
       </c>
       <c r="B17" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>136802878</v>
       </c>
       <c r="B18" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>136802879</v>
       </c>
       <c r="B19" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136802881</v>
       </c>
       <c r="B20" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>136802883</v>
       </c>
       <c r="B21" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>136802884</v>
       </c>
       <c r="B22" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>136802885</v>
       </c>
       <c r="B23" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>136802886</v>
       </c>
       <c r="B24" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136802889</v>
       </c>
       <c r="B25" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>136802857</v>
       </c>
       <c r="B26" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136802865</v>
       </c>
       <c r="B27" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>136802873</v>
       </c>
       <c r="B37" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>136802882</v>
       </c>
       <c r="B38" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>136802872</v>
       </c>
       <c r="B39" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/S 8435-2021 artfynd.xlsx
+++ b/artfynd/S 8435-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136802849</v>
       </c>
       <c r="B2" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136802851</v>
       </c>
       <c r="B3" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>136802854</v>
       </c>
       <c r="B4" t="n">
-        <v>89340</v>
+        <v>89342</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>136802856</v>
       </c>
       <c r="B5" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>136802852</v>
       </c>
       <c r="B6" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>136802853</v>
       </c>
       <c r="B7" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>136802859</v>
       </c>
       <c r="B8" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>136802860</v>
       </c>
       <c r="B9" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>136802862</v>
       </c>
       <c r="B10" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>136802863</v>
       </c>
       <c r="B11" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>136802866</v>
       </c>
       <c r="B12" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>136802868</v>
       </c>
       <c r="B13" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136802870</v>
       </c>
       <c r="B14" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>136802875</v>
       </c>
       <c r="B15" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>136802876</v>
       </c>
       <c r="B16" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>136802877</v>
       </c>
       <c r="B17" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>136802878</v>
       </c>
       <c r="B18" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>136802879</v>
       </c>
       <c r="B19" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136802881</v>
       </c>
       <c r="B20" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>136802883</v>
       </c>
       <c r="B21" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>136802884</v>
       </c>
       <c r="B22" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>136802885</v>
       </c>
       <c r="B23" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>136802886</v>
       </c>
       <c r="B24" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136802889</v>
       </c>
       <c r="B25" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>136802857</v>
       </c>
       <c r="B26" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136802865</v>
       </c>
       <c r="B27" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>136802873</v>
       </c>
       <c r="B37" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>136802882</v>
       </c>
       <c r="B38" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>136802872</v>
       </c>
       <c r="B39" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/S 8435-2021 artfynd.xlsx
+++ b/artfynd/S 8435-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136802849</v>
       </c>
       <c r="B2" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136802851</v>
       </c>
       <c r="B3" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>136802854</v>
       </c>
       <c r="B4" t="n">
-        <v>89342</v>
+        <v>89343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>136802856</v>
       </c>
       <c r="B5" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>136802852</v>
       </c>
       <c r="B6" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>136802853</v>
       </c>
       <c r="B7" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>136802859</v>
       </c>
       <c r="B8" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>136802860</v>
       </c>
       <c r="B9" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>136802862</v>
       </c>
       <c r="B10" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>136802863</v>
       </c>
       <c r="B11" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>136802866</v>
       </c>
       <c r="B12" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>136802868</v>
       </c>
       <c r="B13" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136802870</v>
       </c>
       <c r="B14" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>136802875</v>
       </c>
       <c r="B15" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>136802876</v>
       </c>
       <c r="B16" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>136802877</v>
       </c>
       <c r="B17" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>136802878</v>
       </c>
       <c r="B18" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>136802879</v>
       </c>
       <c r="B19" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136802881</v>
       </c>
       <c r="B20" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>136802883</v>
       </c>
       <c r="B21" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>136802884</v>
       </c>
       <c r="B22" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>136802885</v>
       </c>
       <c r="B23" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>136802886</v>
       </c>
       <c r="B24" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136802889</v>
       </c>
       <c r="B25" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>136802857</v>
       </c>
       <c r="B26" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136802865</v>
       </c>
       <c r="B27" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>136802873</v>
       </c>
       <c r="B37" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>136802882</v>
       </c>
       <c r="B38" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>136802872</v>
       </c>
       <c r="B39" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/S 8435-2021 artfynd.xlsx
+++ b/artfynd/S 8435-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136802849</v>
       </c>
       <c r="B2" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>136802854</v>
       </c>
       <c r="B4" t="n">
-        <v>89343</v>
+        <v>89349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>136802856</v>
       </c>
       <c r="B5" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>136802873</v>
       </c>
       <c r="B37" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>136802882</v>
       </c>
       <c r="B38" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>136802872</v>
       </c>
       <c r="B39" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/S 8435-2021 artfynd.xlsx
+++ b/artfynd/S 8435-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136802849</v>
       </c>
       <c r="B2" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136802851</v>
       </c>
       <c r="B3" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>136802854</v>
       </c>
       <c r="B4" t="n">
-        <v>89349</v>
+        <v>89353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>136802856</v>
       </c>
       <c r="B5" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>136802852</v>
       </c>
       <c r="B6" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>136802853</v>
       </c>
       <c r="B7" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>136802859</v>
       </c>
       <c r="B8" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>136802860</v>
       </c>
       <c r="B9" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>136802862</v>
       </c>
       <c r="B10" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>136802863</v>
       </c>
       <c r="B11" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>136802866</v>
       </c>
       <c r="B12" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>136802868</v>
       </c>
       <c r="B13" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136802870</v>
       </c>
       <c r="B14" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>136802875</v>
       </c>
       <c r="B15" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>136802876</v>
       </c>
       <c r="B16" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>136802877</v>
       </c>
       <c r="B17" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>136802878</v>
       </c>
       <c r="B18" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>136802879</v>
       </c>
       <c r="B19" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136802881</v>
       </c>
       <c r="B20" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>136802883</v>
       </c>
       <c r="B21" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>136802884</v>
       </c>
       <c r="B22" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>136802885</v>
       </c>
       <c r="B23" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>136802886</v>
       </c>
       <c r="B24" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136802889</v>
       </c>
       <c r="B25" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>136802857</v>
       </c>
       <c r="B26" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136802865</v>
       </c>
       <c r="B27" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>136802873</v>
       </c>
       <c r="B37" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>136802882</v>
       </c>
       <c r="B38" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>136802872</v>
       </c>
       <c r="B39" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/S 8435-2021 artfynd.xlsx
+++ b/artfynd/S 8435-2021 artfynd.xlsx
@@ -1087,7 +1087,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Simon Mattsson</t>
+          <t>Simon Mattsson, Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Simon Mattsson</t>
+          <t>Simon Mattsson, Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Simon Mattsson</t>
+          <t>Simon Mattsson, Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Simon Mattsson</t>
+          <t>Simon Mattsson, Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Simon Mattsson</t>
+          <t>Simon Mattsson, Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Simon Mattsson</t>
+          <t>Simon Mattsson, Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Simon Mattsson</t>
+          <t>Simon Mattsson, Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Simon Mattsson</t>
+          <t>Simon Mattsson, Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Simon Mattsson</t>
+          <t>Simon Mattsson, Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Simon Mattsson</t>
+          <t>Simon Mattsson, Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Simon Mattsson</t>
+          <t>Simon Mattsson, Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Simon Mattsson</t>
+          <t>Simon Mattsson, Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Simon Mattsson</t>
+          <t>Simon Mattsson, Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Simon Mattsson</t>
+          <t>Simon Mattsson, Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Simon Mattsson</t>
+          <t>Simon Mattsson, Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Simon Mattsson</t>
+          <t>Simon Mattsson, Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Simon Mattsson</t>
+          <t>Simon Mattsson, Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Simon Mattsson</t>
+          <t>Simon Mattsson, Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/S 8435-2021 artfynd.xlsx
+++ b/artfynd/S 8435-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136802849</v>
       </c>
       <c r="B2" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Andreas Garpebring</t>
+          <t>Andreas Garpebring, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Andreas Garpebring</t>
+          <t>Andreas Garpebring, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Andreas Garpebring</t>
+          <t>Andreas Garpebring, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Andreas Garpebring</t>
+          <t>Andreas Garpebring, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Andreas Garpebring</t>
+          <t>Andreas Garpebring, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Andreas Garpebring</t>
+          <t>Andreas Garpebring, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Andreas Garpebring</t>
+          <t>Andreas Garpebring, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Andreas Garpebring</t>
+          <t>Andreas Garpebring, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Andreas Garpebring</t>
+          <t>Andreas Garpebring, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Andreas Garpebring</t>
+          <t>Andreas Garpebring, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Andreas Garpebring</t>
+          <t>Andreas Garpebring, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Andreas Garpebring</t>
+          <t>Andreas Garpebring, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Andreas Garpebring</t>
+          <t>Andreas Garpebring, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Andreas Garpebring</t>
+          <t>Andreas Garpebring, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Andreas Garpebring</t>
+          <t>Andreas Garpebring, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Andreas Garpebring</t>
+          <t>Andreas Garpebring, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4351,7 +4351,7 @@
         <v>136802873</v>
       </c>
       <c r="B37" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Andreas Garpebring</t>
+          <t>Andreas Garpebring, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4453,7 +4453,7 @@
         <v>136802882</v>
       </c>
       <c r="B38" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>136802872</v>
       </c>
       <c r="B39" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Andreas Garpebring</t>
+          <t>Andreas Garpebring, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/S 8435-2021 artfynd.xlsx
+++ b/artfynd/S 8435-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136802849</v>
       </c>
       <c r="B2" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136802851</v>
       </c>
       <c r="B3" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>136802854</v>
       </c>
       <c r="B4" t="n">
-        <v>89353</v>
+        <v>89355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>136802856</v>
       </c>
       <c r="B5" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>136802852</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>136802853</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>136802859</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>136802860</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>136802862</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>136802863</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>136802866</v>
       </c>
       <c r="B12" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>136802868</v>
       </c>
       <c r="B13" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136802870</v>
       </c>
       <c r="B14" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>136802875</v>
       </c>
       <c r="B15" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>136802876</v>
       </c>
       <c r="B16" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>136802877</v>
       </c>
       <c r="B17" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>136802878</v>
       </c>
       <c r="B18" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>136802879</v>
       </c>
       <c r="B19" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136802881</v>
       </c>
       <c r="B20" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>136802883</v>
       </c>
       <c r="B21" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>136802884</v>
       </c>
       <c r="B22" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>136802885</v>
       </c>
       <c r="B23" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>136802886</v>
       </c>
       <c r="B24" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136802889</v>
       </c>
       <c r="B25" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>136802857</v>
       </c>
       <c r="B26" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136802865</v>
       </c>
       <c r="B27" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>136802873</v>
       </c>
       <c r="B37" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>136802882</v>
       </c>
       <c r="B38" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>136802872</v>
       </c>
       <c r="B39" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/S 8435-2021 artfynd.xlsx
+++ b/artfynd/S 8435-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136802849</v>
       </c>
       <c r="B2" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136802851</v>
       </c>
       <c r="B3" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>136802854</v>
       </c>
       <c r="B4" t="n">
-        <v>89355</v>
+        <v>89368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>136802856</v>
       </c>
       <c r="B5" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>136802852</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>136802853</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>136802859</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>136802860</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>136802862</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>136802863</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>136802866</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>136802868</v>
       </c>
       <c r="B13" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136802870</v>
       </c>
       <c r="B14" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>136802875</v>
       </c>
       <c r="B15" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>136802876</v>
       </c>
       <c r="B16" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>136802877</v>
       </c>
       <c r="B17" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>136802878</v>
       </c>
       <c r="B18" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>136802879</v>
       </c>
       <c r="B19" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136802881</v>
       </c>
       <c r="B20" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>136802883</v>
       </c>
       <c r="B21" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>136802884</v>
       </c>
       <c r="B22" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>136802885</v>
       </c>
       <c r="B23" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>136802886</v>
       </c>
       <c r="B24" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136802889</v>
       </c>
       <c r="B25" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>136802857</v>
       </c>
       <c r="B26" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136802865</v>
       </c>
       <c r="B27" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>136802861</v>
       </c>
       <c r="B29" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>136802867</v>
       </c>
       <c r="B30" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>136802874</v>
       </c>
       <c r="B32" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>136802873</v>
       </c>
       <c r="B37" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>136802882</v>
       </c>
       <c r="B38" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>136802872</v>
       </c>
       <c r="B39" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/S 8435-2021 artfynd.xlsx
+++ b/artfynd/S 8435-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136802849</v>
       </c>
       <c r="B2" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136802851</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>136802854</v>
       </c>
       <c r="B4" t="n">
-        <v>89368</v>
+        <v>89370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>136802856</v>
       </c>
       <c r="B5" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>136802852</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>136802853</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>136802859</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>136802860</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>136802862</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>136802863</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>136802866</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>136802868</v>
       </c>
       <c r="B13" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136802870</v>
       </c>
       <c r="B14" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>136802875</v>
       </c>
       <c r="B15" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>136802876</v>
       </c>
       <c r="B16" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>136802877</v>
       </c>
       <c r="B17" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>136802878</v>
       </c>
       <c r="B18" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>136802879</v>
       </c>
       <c r="B19" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136802881</v>
       </c>
       <c r="B20" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>136802883</v>
       </c>
       <c r="B21" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>136802884</v>
       </c>
       <c r="B22" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>136802885</v>
       </c>
       <c r="B23" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>136802886</v>
       </c>
       <c r="B24" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136802889</v>
       </c>
       <c r="B25" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>136802857</v>
       </c>
       <c r="B26" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136802865</v>
       </c>
       <c r="B27" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>136802861</v>
       </c>
       <c r="B29" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>136802867</v>
       </c>
       <c r="B30" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>136802874</v>
       </c>
       <c r="B32" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>136802873</v>
       </c>
       <c r="B37" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>136802882</v>
       </c>
       <c r="B38" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>136802872</v>
       </c>
       <c r="B39" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/S 8435-2021 artfynd.xlsx
+++ b/artfynd/S 8435-2021 artfynd.xlsx
@@ -3483,16 +3483,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lidmyråsen domänreservat, Vb</t>
@@ -3599,21 +3591,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lidmyråsen domänreservat, Vb</t>
@@ -3716,11 +3696,7 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lidmyråsen domänreservat, Vb</t>
@@ -3832,16 +3808,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lidmyråsen domänreservat, Vb</t>
@@ -3944,11 +3912,7 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lidmyråsen domänreservat, Vb</t>

--- a/artfynd/S 8435-2021 artfynd.xlsx
+++ b/artfynd/S 8435-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136802849</v>
       </c>
       <c r="B2" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>136802854</v>
       </c>
       <c r="B4" t="n">
-        <v>89370</v>
+        <v>89373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>136802856</v>
       </c>
       <c r="B5" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>136802873</v>
       </c>
       <c r="B37" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>136802882</v>
       </c>
       <c r="B38" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>136802872</v>
       </c>
       <c r="B39" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/S 8435-2021 artfynd.xlsx
+++ b/artfynd/S 8435-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136802849</v>
       </c>
       <c r="B2" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136802851</v>
       </c>
       <c r="B3" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>136802854</v>
       </c>
       <c r="B4" t="n">
-        <v>89373</v>
+        <v>89383</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>136802856</v>
       </c>
       <c r="B5" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>136802852</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>136802853</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>136802859</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>136802860</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>136802862</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>136802863</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>136802866</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>136802868</v>
       </c>
       <c r="B13" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136802870</v>
       </c>
       <c r="B14" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>136802875</v>
       </c>
       <c r="B15" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>136802876</v>
       </c>
       <c r="B16" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>136802877</v>
       </c>
       <c r="B17" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>136802878</v>
       </c>
       <c r="B18" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>136802879</v>
       </c>
       <c r="B19" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136802881</v>
       </c>
       <c r="B20" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>136802883</v>
       </c>
       <c r="B21" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>136802884</v>
       </c>
       <c r="B22" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>136802885</v>
       </c>
       <c r="B23" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>136802886</v>
       </c>
       <c r="B24" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136802889</v>
       </c>
       <c r="B25" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>136802857</v>
       </c>
       <c r="B26" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136802865</v>
       </c>
       <c r="B27" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>136802861</v>
       </c>
       <c r="B29" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>136802867</v>
       </c>
       <c r="B30" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>136802880</v>
       </c>
       <c r="B31" t="n">
-        <v>5498</v>
+        <v>5504</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>136802874</v>
       </c>
       <c r="B32" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>136802864</v>
       </c>
       <c r="B33" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>136802873</v>
       </c>
       <c r="B37" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>136802882</v>
       </c>
       <c r="B38" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>136802872</v>
       </c>
       <c r="B39" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/S 8435-2021 artfynd.xlsx
+++ b/artfynd/S 8435-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136802849</v>
       </c>
       <c r="B2" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>136802854</v>
       </c>
       <c r="B4" t="n">
-        <v>89383</v>
+        <v>89384</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>136802856</v>
       </c>
       <c r="B5" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>136802873</v>
       </c>
       <c r="B37" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>136802882</v>
       </c>
       <c r="B38" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>136802872</v>
       </c>
       <c r="B39" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/S 8435-2021 artfynd.xlsx
+++ b/artfynd/S 8435-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136802849</v>
       </c>
       <c r="B2" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136802851</v>
       </c>
       <c r="B3" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>136802854</v>
       </c>
       <c r="B4" t="n">
-        <v>89384</v>
+        <v>89387</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>136802856</v>
       </c>
       <c r="B5" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>136802852</v>
       </c>
       <c r="B6" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>136802853</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>136802859</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>136802860</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>136802862</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>136802863</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>136802866</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>136802868</v>
       </c>
       <c r="B13" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136802870</v>
       </c>
       <c r="B14" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>136802875</v>
       </c>
       <c r="B15" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>136802876</v>
       </c>
       <c r="B16" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>136802877</v>
       </c>
       <c r="B17" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>136802878</v>
       </c>
       <c r="B18" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>136802879</v>
       </c>
       <c r="B19" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136802881</v>
       </c>
       <c r="B20" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>136802883</v>
       </c>
       <c r="B21" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>136802884</v>
       </c>
       <c r="B22" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>136802885</v>
       </c>
       <c r="B23" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>136802886</v>
       </c>
       <c r="B24" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136802889</v>
       </c>
       <c r="B25" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>136802857</v>
       </c>
       <c r="B26" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136802865</v>
       </c>
       <c r="B27" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>136802861</v>
       </c>
       <c r="B29" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>136802867</v>
       </c>
       <c r="B30" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>136802874</v>
       </c>
       <c r="B32" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>136802873</v>
       </c>
       <c r="B37" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>136802882</v>
       </c>
       <c r="B38" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>136802872</v>
       </c>
       <c r="B39" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/S 8435-2021 artfynd.xlsx
+++ b/artfynd/S 8435-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136802849</v>
       </c>
       <c r="B2" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>136802856</v>
       </c>
       <c r="B5" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>136802873</v>
       </c>
       <c r="B37" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>136802882</v>
       </c>
       <c r="B38" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>136802872</v>
       </c>
       <c r="B39" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/S 8435-2021 artfynd.xlsx
+++ b/artfynd/S 8435-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136802849</v>
       </c>
       <c r="B2" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136802851</v>
       </c>
       <c r="B3" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>136802854</v>
       </c>
       <c r="B4" t="n">
-        <v>89387</v>
+        <v>89392</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>136802856</v>
       </c>
       <c r="B5" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>136802852</v>
       </c>
       <c r="B6" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>136802853</v>
       </c>
       <c r="B7" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>136802859</v>
       </c>
       <c r="B8" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>136802860</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>136802862</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>136802863</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>136802866</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>136802868</v>
       </c>
       <c r="B13" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136802870</v>
       </c>
       <c r="B14" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>136802875</v>
       </c>
       <c r="B15" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>136802876</v>
       </c>
       <c r="B16" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>136802877</v>
       </c>
       <c r="B17" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>136802878</v>
       </c>
       <c r="B18" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>136802879</v>
       </c>
       <c r="B19" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136802881</v>
       </c>
       <c r="B20" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>136802883</v>
       </c>
       <c r="B21" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>136802884</v>
       </c>
       <c r="B22" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>136802885</v>
       </c>
       <c r="B23" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>136802886</v>
       </c>
       <c r="B24" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136802889</v>
       </c>
       <c r="B25" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>136802857</v>
       </c>
       <c r="B26" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136802865</v>
       </c>
       <c r="B27" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>136802861</v>
       </c>
       <c r="B29" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>136802867</v>
       </c>
       <c r="B30" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>136802873</v>
       </c>
       <c r="B37" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>136802882</v>
       </c>
       <c r="B38" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>136802872</v>
       </c>
       <c r="B39" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
